--- a/crc39_CondicionesEspeciales.xlsx
+++ b/crc39_CondicionesEspeciales.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tuitconosultant-my.sharepoint.com/personal/info_sumtransportes_com1/Documents/SUM MIGUEL/miguel/miaplicacionlogistica/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3641" documentId="6_{4BDD1192-46BC-4A3C-A432-4C879C250D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F443AA38-ABD8-42D7-BF86-7C076FEFB597}"/>
+  <xr:revisionPtr revIDLastSave="3664" documentId="6_{4BDD1192-46BC-4A3C-A432-4C879C250D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45CD7362-FAC9-4378-9CB2-31FFD4F05B74}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="-15312" yWindow="4116" windowWidth="7500" windowHeight="6000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="20940" yWindow="2532" windowWidth="7500" windowHeight="6000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Condiciones Especiales" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3392" uniqueCount="677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3396" uniqueCount="677">
   <si>
     <t>Descripción Cliente</t>
   </si>
@@ -1808,9 +1808,6 @@
     <t>{"@odata.etag":"W/\"559448285\"","modifiedon@OData.Community.Display.V1.FormattedValue":"06/02/2026 9:49","modifiedon":"2026-02-06T08:49:12Z","crc39_codigodearticulo":"1","overriddencreatedon":null,"crc39_descripcioncliente":"ESMEBRA S.L.","importsequencenumber":null,"crc39_name":null,"crc39_clientearticulo":"ESMEBRA S.L.BLT_1","_modifiedonbehalfby_value":null,"statecode@OData.Community.Display.V1.FormattedValue":"Activo","statecode":0,"crc39_condicionesespecialesid":"3a46f0dd-41d7-ea11-a813-000d3a4684b2","versionnumber@OData.Community.Display.V1.FormattedValue":"559.448.285","versionnumber":559448285,"crc39_precioespecial@OData.Community.Display.V1.FormattedValue":"6,00","crc39_precioespecial":6,"crc39_codigocliente":"244","utcconversiontimezonecode":null,"_createdonbehalfby_value":null,"_modifiedby_value@OData.Community.Display.V1.FormattedValue":"SUM Transportes","_modifiedby_value@Microsoft.Dynamics.CRM.lookuplogicalname":"systemuser","_modifiedby_value":"36fe0121-0ab0-4631-8342-ebfb6b988259","createdon@OData.Community.Display.V1.FormattedValue":"05/08/2020 18:34","createdon":"2020-08-05T17:34:11Z","_owningbusinessunit_value@OData.Community.Display.V1.FormattedValue":"org4bb1ce1c","_owningbusinessunit_value@Microsoft.Dynamics.CRM.associatednavigationproperty":"owningbusinessunit","_owningbusinessunit_value@Microsoft.Dynamics.CRM.lookuplogicalname":"businessunit","_owningbusinessunit_value":"f647125d-9b19-ea11-a811-000d3a294985","crc39_descripcionarticulo":"BLT_1","statuscode@OData.Community.Display.V1.FormattedValue":"Activo","statuscode":1,"_owningteam_value":null,"_createdby_value@OData.Community.Display.V1.FormattedValue":"SUM Transportes","_createdby_value@Microsoft.Dynamics.CRM.lookuplogicalname":"systemuser","_createdby_value":"36fe0121-0ab0-4631-8342-ebfb6b988259","_ownerid_value@OData.Community.Display.V1.FormattedValue":"SUM Transportes","_ownerid_value@Microsoft.Dynamics.CRM.associatednavigationproperty":"ownerid","_ownerid_value@Microsoft.Dynamics.CRM.lookuplogicalname":"systemuser","_ownerid_value":"36fe0121-0ab0-4631-8342-ebfb6b988259","timezoneruleversionnumber":null,"_createdby_display":"SUM Transportes","_owningbusinessunit_display":"org4bb1ce1c","_modifiedby_display":"SUM Transportes","_ownerid_display":"SUM Transportes"}</t>
   </si>
   <si>
-    <t>{"@odata.etag":"W/\"559448286\"","modifiedon@OData.Community.Display.V1.FormattedValue":"06/02/2026 9:49","modifiedon":"2026-02-06T08:49:12Z","crc39_codigodearticulo":"2","overriddencreatedon":null,"crc39_descripcioncliente":"ESMEBRA S.L.","importsequencenumber":null,"crc39_name":null,"crc39_clientearticulo":"ESMEBRA S.L.BLT_2","_modifiedonbehalfby_value":null,"statecode@OData.Community.Display.V1.FormattedValue":"Activo","statecode":0,"crc39_condicionesespecialesid":"3b46f0dd-41d7-ea11-a813-000d3a4684b2","versionnumber@OData.Community.Display.V1.FormattedValue":"559.448.286","versionnumber":559448286,"crc39_precioespecial@OData.Community.Display.V1.FormattedValue":"11,00","crc39_precioespecial":11,"crc39_codigocliente":"244","utcconversiontimezonecode":null,"_createdonbehalfby_value":null,"_modifiedby_value@OData.Community.Display.V1.FormattedValue":"SUM Transportes","_modifiedby_value@Microsoft.Dynamics.CRM.lookuplogicalname":"systemuser","_modifiedby_value":"36fe0121-0ab0-4631-8342-ebfb6b988259","createdon@OData.Community.Display.V1.FormattedValue":"05/08/2020 18:34","createdon":"2020-08-05T17:34:11Z","_owningbusinessunit_value@OData.Community.Display.V1.FormattedValue":"org4bb1ce1c","_owningbusinessunit_value@Microsoft.Dynamics.CRM.associatednavigationproperty":"owningbusinessunit","_owningbusinessunit_value@Microsoft.Dynamics.CRM.lookuplogicalname":"businessunit","_owningbusinessunit_value":"f647125d-9b19-ea11-a811-000d3a294985","crc39_descripcionarticulo":"BLT_2","statuscode@OData.Community.Display.V1.FormattedValue":"Activo","statuscode":1,"_owningteam_value":null,"_createdby_value@OData.Community.Display.V1.FormattedValue":"SUM Transportes","_createdby_value@Microsoft.Dynamics.CRM.lookuplogicalname":"systemuser","_createdby_value":"36fe0121-0ab0-4631-8342-ebfb6b988259","_ownerid_value@OData.Community.Display.V1.FormattedValue":"SUM Transportes","_ownerid_value@Microsoft.Dynamics.CRM.associatednavigationproperty":"ownerid","_ownerid_value@Microsoft.Dynamics.CRM.lookuplogicalname":"systemuser","_ownerid_value":"36fe0121-0ab0-4631-8342-ebfb6b988259","timezoneruleversionnumber":null,"_createdby_display":"SUM Transportes","_owningbusinessunit_display":"org4bb1ce1c","_modifiedby_display":"SUM Transportes","_ownerid_display":"SUM Transportes"}</t>
-  </si>
-  <si>
     <t>{"@odata.etag":"W/\"559448287\"","modifiedon@OData.Community.Display.V1.FormattedValue":"06/02/2026 9:49","modifiedon":"2026-02-06T08:49:13Z","crc39_codigodearticulo":"3","overriddencreatedon":null,"crc39_descripcioncliente":"ESMEBRA S.L.","importsequencenumber":null,"crc39_name":null,"crc39_clientearticulo":"ESMEBRA S.L.BLT_3","_modifiedonbehalfby_value":null,"statecode@OData.Community.Display.V1.FormattedValue":"Activo","statecode":0,"crc39_condicionesespecialesid":"3c46f0dd-41d7-ea11-a813-000d3a4684b2","versionnumber@OData.Community.Display.V1.FormattedValue":"559.448.287","versionnumber":559448287,"crc39_precioespecial@OData.Community.Display.V1.FormattedValue":"15,00","crc39_precioespecial":15,"crc39_codigocliente":"244","utcconversiontimezonecode":null,"_createdonbehalfby_value":null,"_modifiedby_value@OData.Community.Display.V1.FormattedValue":"SUM Transportes","_modifiedby_value@Microsoft.Dynamics.CRM.lookuplogicalname":"systemuser","_modifiedby_value":"36fe0121-0ab0-4631-8342-ebfb6b988259","createdon@OData.Community.Display.V1.FormattedValue":"05/08/2020 18:34","createdon":"2020-08-05T17:34:11Z","_owningbusinessunit_value@OData.Community.Display.V1.FormattedValue":"org4bb1ce1c","_owningbusinessunit_value@Microsoft.Dynamics.CRM.associatednavigationproperty":"owningbusinessunit","_owningbusinessunit_value@Microsoft.Dynamics.CRM.lookuplogicalname":"businessunit","_owningbusinessunit_value":"f647125d-9b19-ea11-a811-000d3a294985","crc39_descripcionarticulo":"BLT_3","statuscode@OData.Community.Display.V1.FormattedValue":"Activo","statuscode":1,"_owningteam_value":null,"_createdby_value@OData.Community.Display.V1.FormattedValue":"SUM Transportes","_createdby_value@Microsoft.Dynamics.CRM.lookuplogicalname":"systemuser","_createdby_value":"36fe0121-0ab0-4631-8342-ebfb6b988259","_ownerid_value@OData.Community.Display.V1.FormattedValue":"SUM Transportes","_ownerid_value@Microsoft.Dynamics.CRM.associatednavigationproperty":"ownerid","_ownerid_value@Microsoft.Dynamics.CRM.lookuplogicalname":"systemuser","_ownerid_value":"36fe0121-0ab0-4631-8342-ebfb6b988259","timezoneruleversionnumber":null,"_createdby_display":"SUM Transportes","_owningbusinessunit_display":"org4bb1ce1c","_modifiedby_display":"SUM Transportes","_ownerid_display":"SUM Transportes"}</t>
   </si>
   <si>
@@ -2087,7 +2084,10 @@
     <t>eb96d058-ec4d-f111-bec7-7c1e5283c1c8</t>
   </si>
   <si>
-    <t>{"@odata.context":"https://org3210d160.crm4.dynamics.com/api/data/v9.0/$metadata#crc39_condicionesespecialeses/$entity","@odata.etag":"W/\"560378981\"","modifiedon":"2026-05-12T10:21:33Z","_owninguser_value":"36fe0121-0ab0-4631-8342-ebfb6b988259","crc39_codigodearticulo":null,"overriddencreatedon":null,"crc39_descripcioncliente":"CORECO","importsequencenumber":null,"crc39_name":null,"crc39_clientearticulo":"CORECOBLT_1","_modifiedonbehalfby_value":null,"statecode":0,"crc39_condicionesespecialesid":"eb96d058-ec4d-f111-bec7-7c1e5283c1c8","versionnumber":560378981,"crc39_precioespecial":6.5,"crc39_codigocliente":null,"utcconversiontimezonecode":null,"_createdonbehalfby_value":null,"_modifiedby_value":"36fe0121-0ab0-4631-8342-ebfb6b988259","createdon":"2026-05-12T10:21:33Z","_owningbusinessunit_value":"f647125d-9b19-ea11-a811-000d3a294985","crc39_descripcionarticulo":"BLT_1","statuscode":1,"_owningteam_value":null,"_createdby_value":"36fe0121-0ab0-4631-8342-ebfb6b988259","_ownerid_value":"36fe0121-0ab0-4631-8342-ebfb6b988259","timezoneruleversionnumber":null}</t>
+    <t>{"@odata.etag":"W/\"560378981\"","modifiedon@OData.Community.Display.V1.FormattedValue":"12/05/2026 11:21","modifiedon":"2026-05-12T10:21:33Z","crc39_codigodearticulo":null,"overriddencreatedon":null,"crc39_descripcioncliente":"CORECO","importsequencenumber":null,"crc39_name":null,"crc39_clientearticulo":"CORECOBLT_1","_modifiedonbehalfby_value":null,"statecode@OData.Community.Display.V1.FormattedValue":"Activo","statecode":0,"crc39_condicionesespecialesid":"eb96d058-ec4d-f111-bec7-7c1e5283c1c8","versionnumber@OData.Community.Display.V1.FormattedValue":"560.378.981","versionnumber":560378981,"crc39_precioespecial@OData.Community.Display.V1.FormattedValue":"6,50","crc39_precioespecial":6.5,"crc39_codigocliente":null,"utcconversiontimezonecode":null,"_createdonbehalfby_value":null,"_modifiedby_value@OData.Community.Display.V1.FormattedValue":"SUM Transportes","_modifiedby_value@Microsoft.Dynamics.CRM.lookuplogicalname":"systemuser","_modifiedby_value":"36fe0121-0ab0-4631-8342-ebfb6b988259","createdon@OData.Community.Display.V1.FormattedValue":"12/05/2026 11:21","createdon":"2026-05-12T10:21:33Z","_owningbusinessunit_value@OData.Community.Display.V1.FormattedValue":"org4bb1ce1c","_owningbusinessunit_value@Microsoft.Dynamics.CRM.associatednavigationproperty":"owningbusinessunit","_owningbusinessunit_value@Microsoft.Dynamics.CRM.lookuplogicalname":"businessunit","_owningbusinessunit_value":"f647125d-9b19-ea11-a811-000d3a294985","crc39_descripcionarticulo":"BLT_1","statuscode@OData.Community.Display.V1.FormattedValue":"Activo","statuscode":1,"_owningteam_value":null,"_createdby_value@OData.Community.Display.V1.FormattedValue":"SUM Transportes","_createdby_value@Microsoft.Dynamics.CRM.lookuplogicalname":"systemuser","_createdby_value":"36fe0121-0ab0-4631-8342-ebfb6b988259","_ownerid_value@OData.Community.Display.V1.FormattedValue":"SUM Transportes","_ownerid_value@Microsoft.Dynamics.CRM.associatednavigationproperty":"ownerid","_ownerid_value@Microsoft.Dynamics.CRM.lookuplogicalname":"systemuser","_ownerid_value":"36fe0121-0ab0-4631-8342-ebfb6b988259","timezoneruleversionnumber":null,"_createdby_display":"SUM Transportes","_owningbusinessunit_display":"org4bb1ce1c","_modifiedby_display":"SUM Transportes","_ownerid_display":"SUM Transportes"}</t>
+  </si>
+  <si>
+    <t>{"@odata.context":"https://org3210d160.crm4.dynamics.com/api/data/v9.0/$metadata#crc39_condicionesespecialeses/$entity","@odata.etag":"W/\"561029828\"","modifiedon@OData.Community.Display.V1.FormattedValue":"05/08/2026 12:09","modifiedon":"2026-08-05T11:09:50Z","_owninguser_value@Microsoft.Dynamics.CRM.lookuplogicalname":"systemuser","_owninguser_value":"36fe0121-0ab0-4631-8342-ebfb6b988259","crc39_codigodearticulo":"2","overriddencreatedon":null,"crc39_descripcioncliente":"ESMEBRA S.L.","importsequencenumber":null,"crc39_name":null,"crc39_clientearticulo":"ESMEBRA S.L.BLT_2","_modifiedonbehalfby_value":null,"statecode@OData.Community.Display.V1.FormattedValue":"Activo","statecode":0,"crc39_condicionesespecialesid":"3b46f0dd-41d7-ea11-a813-000d3a4684b2","versionnumber@OData.Community.Display.V1.FormattedValue":"561.029.828","versionnumber":561029828,"crc39_precioespecial@OData.Community.Display.V1.FormattedValue":"10,00","crc39_precioespecial":10,"crc39_codigocliente":"244","utcconversiontimezonecode":null,"_createdonbehalfby_value":null,"_modifiedby_value@OData.Community.Display.V1.FormattedValue":"SUM Transportes","_modifiedby_value@Microsoft.Dynamics.CRM.lookuplogicalname":"systemuser","_modifiedby_value":"36fe0121-0ab0-4631-8342-ebfb6b988259","createdon@OData.Community.Display.V1.FormattedValue":"05/08/2020 18:34","createdon":"2020-08-05T17:34:11Z","_owningbusinessunit_value@OData.Community.Display.V1.FormattedValue":"org4bb1ce1c","_owningbusinessunit_value@Microsoft.Dynamics.CRM.associatednavigationproperty":"owningbusinessunit","_owningbusinessunit_value@Microsoft.Dynamics.CRM.lookuplogicalname":"businessunit","_owningbusinessunit_value":"f647125d-9b19-ea11-a811-000d3a294985","crc39_descripcionarticulo":"BLT_2","statuscode@OData.Community.Display.V1.FormattedValue":"Activo","statuscode":1,"_owningteam_value":null,"_createdby_value@OData.Community.Display.V1.FormattedValue":"SUM Transportes","_createdby_value@Microsoft.Dynamics.CRM.lookuplogicalname":"systemuser","_createdby_value":"36fe0121-0ab0-4631-8342-ebfb6b988259","_ownerid_value@OData.Community.Display.V1.FormattedValue":"SUM Transportes","_ownerid_value@Microsoft.Dynamics.CRM.associatednavigationproperty":"ownerid","_ownerid_value@Microsoft.Dynamics.CRM.lookuplogicalname":"systemuser","_ownerid_value":"36fe0121-0ab0-4631-8342-ebfb6b988259","timezoneruleversionnumber":null,"_createdby_display":"SUM Transportes","_owningbusinessunit_display":"org4bb1ce1c","_modifiedby_display":"SUM Transportes","_ownerid_display":"SUM Transportes"}</t>
   </si>
 </sst>
 </file>
@@ -3004,7 +3004,7 @@
     </row>
     <row r="5" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>51</v>
@@ -3022,7 +3022,7 @@
         <v>34</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>500</v>
@@ -3059,7 +3059,7 @@
         <v>38</v>
       </c>
       <c r="Y5" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="Z5" s="2" t="s">
         <v>40</v>
@@ -3085,7 +3085,7 @@
     </row>
     <row r="6" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>32</v>
@@ -3103,7 +3103,7 @@
         <v>34</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>500</v>
@@ -3140,7 +3140,7 @@
         <v>38</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="Z6" s="2" t="s">
         <v>40</v>
@@ -3166,7 +3166,7 @@
     </row>
     <row r="7" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>42</v>
@@ -3184,7 +3184,7 @@
         <v>34</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>500</v>
@@ -3221,7 +3221,7 @@
         <v>38</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="Z7" s="2" t="s">
         <v>40</v>
@@ -3247,7 +3247,7 @@
     </row>
     <row r="8" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>46</v>
@@ -3265,7 +3265,7 @@
         <v>34</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>500</v>
@@ -3302,7 +3302,7 @@
         <v>38</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="Z8" s="2" t="s">
         <v>40</v>
@@ -7870,7 +7870,7 @@
         <v>32</v>
       </c>
       <c r="D65" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>500</v>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="P65" s="4"/>
       <c r="Q65" s="4">
-        <v>46059.3675</v>
+        <v>46239.465162037035</v>
       </c>
       <c r="R65" s="3" t="s">
         <v>34</v>
@@ -7909,7 +7909,7 @@
       <c r="S65" s="3"/>
       <c r="T65" s="6"/>
       <c r="U65" s="6">
-        <v>559448286</v>
+        <v>561029828</v>
       </c>
       <c r="V65" s="6"/>
       <c r="W65" s="2" t="s">
@@ -15883,7 +15883,7 @@
     </row>
     <row r="164" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B164" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>51</v>
@@ -15897,9 +15897,11 @@
       <c r="F164" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G164" s="3"/>
+      <c r="G164" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="H164" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="I164" s="2" t="s">
         <v>500</v>
@@ -15907,7 +15909,9 @@
       <c r="J164" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="K164" s="3"/>
+      <c r="K164" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="L164" s="3"/>
       <c r="M164" s="6"/>
       <c r="N164" s="3"/>
@@ -15918,7 +15922,9 @@
       <c r="Q164" s="4">
         <v>46154.431631944448</v>
       </c>
-      <c r="R164" s="3"/>
+      <c r="R164" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="S164" s="3"/>
       <c r="T164" s="6"/>
       <c r="U164" s="6">
@@ -15928,9 +15934,11 @@
       <c r="W164" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="X164" s="3"/>
+      <c r="X164" s="3" t="s">
+        <v>38</v>
+      </c>
       <c r="Y164" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="Z164" s="2" t="s">
         <v>40</v>
@@ -16013,22 +16021,22 @@
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -16313,62 +16321,62 @@
     </row>
     <row r="63" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D63" t="s">
-        <v>583</v>
+        <v>676</v>
       </c>
     </row>
     <row r="64" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D64" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="65" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D65" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="66" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D66" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="67" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="68" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D68" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="69" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D69" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="70" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D70" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="71" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D71" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="72" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D72" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="73" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D73" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="74" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D74" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="75" spans="4:4" x14ac:dyDescent="0.3">
@@ -16388,27 +16396,27 @@
     </row>
     <row r="78" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D78" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="79" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D79" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="80" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D80" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="81" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D81" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="82" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D82" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="83" spans="4:4" x14ac:dyDescent="0.3">
@@ -16418,32 +16426,32 @@
     </row>
     <row r="84" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D84" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="85" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D85" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="86" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D86" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="87" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D87" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="88" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D88" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="89" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D89" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="90" spans="4:4" x14ac:dyDescent="0.3">
@@ -16453,42 +16461,42 @@
     </row>
     <row r="91" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D91" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="92" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D92" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="93" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D93" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="94" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D94" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="95" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D95" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="96" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D96" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="97" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D97" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="98" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D98" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="99" spans="4:4" x14ac:dyDescent="0.3">
@@ -16508,42 +16516,42 @@
     </row>
     <row r="102" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D102" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="103" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D103" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="104" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D104" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="105" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D105" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="106" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D106" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="107" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D107" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="108" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D108" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="109" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D109" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="110" spans="4:4" x14ac:dyDescent="0.3">
@@ -16553,82 +16561,82 @@
     </row>
     <row r="111" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D111" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="112" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D112" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="113" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D113" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="114" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D114" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="115" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D115" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="116" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D116" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="117" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D117" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="118" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D118" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="119" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D119" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="120" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D120" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="121" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D121" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="122" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D122" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="123" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D123" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="124" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D124" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="125" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D125" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="126" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D126" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="127" spans="4:4" x14ac:dyDescent="0.3">
@@ -16648,62 +16656,62 @@
     </row>
     <row r="130" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D130" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="131" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D131" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="132" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D132" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="133" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D133" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="134" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D134" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="135" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D135" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="136" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D136" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="137" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D137" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="138" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D138" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="139" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D139" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="140" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D140" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="141" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D141" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="142" spans="4:4" x14ac:dyDescent="0.3">
@@ -16723,7 +16731,7 @@
     </row>
     <row r="145" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D145" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="146" spans="4:4" x14ac:dyDescent="0.3">
@@ -16763,52 +16771,52 @@
     </row>
     <row r="153" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D153" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="154" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D154" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="155" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D155" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="156" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D156" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="157" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D157" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="158" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D158" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="159" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D159" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="160" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D160" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="161" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D161" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="162" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D162" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
   </sheetData>
